--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104574_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104574_W13.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9719</v>
+        <v>2.4173</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8146</v>
+        <v>1.6172</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1573</v>
+        <v>0.8001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9463</v>
+        <v>0.8753</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5757</v>
+        <v>0.3014</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3706</v>
+        <v>0.5739</v>
       </c>
       <c r="J2" t="n">
-        <v>1.737</v>
+        <v>1.0458</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6624</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.1117</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.1704</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0867</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2959</v>
+        <v>0.4622</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9575</v>
+        <v>-0.4109</v>
       </c>
       <c r="T2" t="n">
-        <v>0.983</v>
+        <v>-0.4207</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0254</v>
+        <v>0.0097</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1607</v>
+        <v>2.4082</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3214</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6002</v>
+        <v>2.2191</v>
       </c>
       <c r="E3" t="n">
-        <v>1.459</v>
+        <v>3.7714</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1411</v>
+        <v>-1.5522</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8638</v>
+        <v>1.1832</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2986</v>
+        <v>0.7556</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5652</v>
+        <v>0.4276</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0573</v>
+        <v>2.1144</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9453</v>
+        <v>1.6752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.112</v>
+        <v>0.4392</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1935</v>
+        <v>-0.9312</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.9196</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4532</v>
+        <v>-0.0116</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2202</v>
+        <v>0.0359</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6079</v>
+        <v>0.0926</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3877</v>
+        <v>-0.0567</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4102</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>3.278</v>
+        <v>1.792</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8678</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1672</v>
+        <v>2.207</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2932</v>
+        <v>0.0609</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8741</v>
+        <v>2.146</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0335</v>
+        <v>0.0373</v>
       </c>
       <c r="H4" t="n">
-        <v>0.58</v>
+        <v>0.5856</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5464</v>
+        <v>-0.5483</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8389</v>
+        <v>-0.8541</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8724</v>
+        <v>0.8914</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5468</v>
+        <v>-0.5133</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0393</v>
+        <v>-0.1745</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5861</v>
+        <v>-0.3388</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3368</v>
+        <v>2.1566</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2573</v>
+        <v>2.1651</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9204</v>
+        <v>-0.0086</v>
       </c>
       <c r="G5" t="n">
-        <v>1.187</v>
+        <v>0.9559</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7605</v>
+        <v>0.5772</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4265</v>
+        <v>0.3787</v>
       </c>
       <c r="J5" t="n">
-        <v>2.135</v>
+        <v>1.7292</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6899</v>
+        <v>1.6547</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4451</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.948</v>
+        <v>-0.7733</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9294</v>
+        <v>-1.0775</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0186</v>
+        <v>0.3043</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8502</v>
+        <v>0.1323</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4506</v>
+        <v>0.348</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3995</v>
+        <v>-0.2157</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.5074</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3927</v>
+        <v>2.2462</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1844</v>
+        <v>-2.7536</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2751</v>
+        <v>0.595</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3002</v>
+        <v>-2.0591</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5753</v>
+        <v>2.6541</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2878</v>
+        <v>1.4276</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7171</v>
+        <v>-0.4934</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0048</v>
+        <v>1.921</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0126</v>
+        <v>-0.8326</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5831</v>
+        <v>-1.5658</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5705</v>
+        <v>0.7331</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5580000000000001</v>
+        <v>-0.3496</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>-0.697</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4673</v>
+        <v>0.3474</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8639</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7712</v>
+        <v>2.8814</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7216</v>
+        <v>-0.7708</v>
       </c>
       <c r="E7" t="n">
-        <v>2.15</v>
+        <v>-0.0534</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8715</v>
+        <v>-0.7174</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6066</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0562</v>
+        <v>-0.1868</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6628</v>
+        <v>0.1952</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4533</v>
+        <v>0.0372</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4818</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9351</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8467</v>
+        <v>-0.0289</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5744</v>
+        <v>-0.1868</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7277</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5816</v>
+        <v>0.2404</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8347</v>
+        <v>-0.0907</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2531</v>
+        <v>0.3311</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8924</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7317</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7497</v>
+        <v>-0.8253</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2409</v>
+        <v>-0.5018</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5088</v>
+        <v>-0.3235</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0055</v>
+        <v>0.2774</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1891</v>
+        <v>-1.2956</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1946</v>
+        <v>1.5729</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0373</v>
+        <v>0.277</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.7207</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.9977</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0318</v>
+        <v>0.0003</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1891</v>
+        <v>-0.5749</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.5752</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2713</v>
+        <v>0.3055</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2782</v>
+        <v>-0.0049</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5495</v>
+        <v>0.3104</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2534</v>
+        <v>-1.8634</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5162</v>
+        <v>-1.1201</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5739</v>
+        <v>-1.2757</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0576</v>
+        <v>0.1556</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2129</v>
+        <v>-1.2165</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2612</v>
+        <v>0.2613</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4741</v>
+        <v>-1.4779</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2956</v>
+        <v>-1.3035</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0828</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5302</v>
+        <v>-0.1312</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>0.0278</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.056</v>
+        <v>-2.0479</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3149</v>
+        <v>-3.3746</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2589</v>
+        <v>1.3266</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6525</v>
+        <v>-4.4033</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7892</v>
+        <v>-2.033</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4417</v>
+        <v>-2.3702</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3177</v>
+        <v>-3.6027</v>
       </c>
       <c r="K10" t="n">
-        <v>1.42</v>
+        <v>-0.8833</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.7377</v>
+        <v>-2.7194</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3348</v>
+        <v>-0.8006</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6308</v>
+        <v>-1.1497</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2959</v>
+        <v>0.3492</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5622</v>
+        <v>-0.8024</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1785</v>
+        <v>-0.3558</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7407</v>
+        <v>-0.4466</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3856</v>
+        <v>1.792</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.9497</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7071</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2956</v>
+        <v>-2.4489</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7408</v>
+        <v>-2.7046</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4452</v>
+        <v>0.2556</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3902</v>
+        <v>-1.6571</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0258</v>
+        <v>0.7952</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3644</v>
+        <v>-2.4524</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.56</v>
+        <v>-1.3432</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8596</v>
+        <v>1.4134</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7003</v>
+        <v>-2.7566</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8302</v>
+        <v>-0.3139</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1662</v>
+        <v>-0.6182</v>
       </c>
       <c r="O11" t="n">
-        <v>0.336</v>
+        <v>0.3043</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0661</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7803</v>
+        <v>-0.1745</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2858</v>
+        <v>-0.7766</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7997</v>
+        <v>0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>1.9604</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7991</v>
+        <v>-3.7149</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2228</v>
+        <v>-4.6521</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4236</v>
+        <v>0.9372</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1532</v>
+        <v>-1.1402</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8919</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2612</v>
+        <v>-0.2607</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6325</v>
+        <v>-0.6542</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4951</v>
+        <v>0.4859</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5206</v>
+        <v>-0.486</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.387</v>
+        <v>-1.3654</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8313</v>
+        <v>-0.7537</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9194</v>
+        <v>-0.3071</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9119</v>
+        <v>-0.4466</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8636</v>
+        <v>-5.0331</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3952</v>
+        <v>-4.4658</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4683</v>
+        <v>-0.5673</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.8496</v>
+        <v>-3.845</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7835</v>
+        <v>-2.7831</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0662</v>
+        <v>-1.0619</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3235</v>
+        <v>-2.3401</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6491</v>
+        <v>-1.6622</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5261</v>
+        <v>-1.5048</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2129</v>
+        <v>0.0395</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1966</v>
+        <v>0.1506</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0163</v>
+        <v>-0.1111</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.502800000000001</v>
+        <v>-7.468400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.907100000000002</v>
+        <v>-7.1672</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5956000000000001</v>
+        <v>-0.3015</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.3406</v>
+        <v>-8.329600000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.9815</v>
+        <v>-5.9608</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.359000000000001</v>
+        <v>-2.369</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.2605</v>
+        <v>-3.466600000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6307</v>
+        <v>3.524</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.8912</v>
+        <v>-6.990700000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.0799</v>
+        <v>-4.863</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.6122</v>
+        <v>-9.4848</v>
       </c>
       <c r="O14" t="n">
-        <v>4.532</v>
+        <v>4.6219</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1341</v>
+        <v>1.1381</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.744</v>
+        <v>-14.796</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.188899999999999</v>
+        <v>-3.1586</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.6612</v>
+        <v>-1.6062</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5274</v>
+        <v>-1.5525</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8923</v>
+        <v>2.881699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>12.7588</v>
+        <v>12.7016</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.866500000000002</v>
+        <v>-9.8202</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0447</v>
+        <v>7.0559</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1445</v>
+        <v>4.6492</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9001</v>
+        <v>2.4067</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9155</v>
+        <v>2.919</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3823</v>
+        <v>2.381</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5331</v>
+        <v>0.538</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9762</v>
+        <v>1.9551</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8399</v>
+        <v>2.8268</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8637</v>
+        <v>-0.8718</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9392</v>
+        <v>0.9639</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2219</v>
+        <v>1.2264</v>
       </c>
       <c r="T15" t="n">
-        <v>0.983</v>
+        <v>0.5152</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2389</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6614</v>
+        <v>4.603</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5943</v>
+        <v>3.8847</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0671</v>
+        <v>0.7183</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9277</v>
+        <v>1.6321</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5541</v>
+        <v>2.1714</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6264</v>
+        <v>-0.5393</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2521</v>
+        <v>0.4377</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9021</v>
+        <v>2.3302</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.6501</v>
+        <v>-1.8925</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6757</v>
+        <v>1.1944</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.348</v>
+        <v>-0.1588</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0237</v>
+        <v>1.3532</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0117</v>
+        <v>0.8814</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1815</v>
+        <v>0.2759</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8302</v>
+        <v>0.6055</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>5.4474</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7071</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3758</v>
+        <v>4.5559</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8502999999999999</v>
+        <v>1.4449</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5255</v>
+        <v>3.1109</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2116</v>
+        <v>1.9266</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0174</v>
+        <v>2.5506</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1942</v>
+        <v>-0.624</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9102</v>
+        <v>1.2204</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7982</v>
+        <v>2.8818</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>-1.6614</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3015</v>
+        <v>0.7062</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2192</v>
+        <v>-0.3312</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0823</v>
+        <v>1.0374</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.722</v>
+        <v>2.2763</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9503</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3803</v>
+        <v>0.0668</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.831</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0965</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3726</v>
+        <v>2.7144</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5847</v>
+        <v>-0.8426</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2121</v>
+        <v>3.5571</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6347</v>
+        <v>4.2132</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1731</v>
+        <v>3.0076</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5384</v>
+        <v>1.2056</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4713</v>
+        <v>2.8901</v>
       </c>
       <c r="K18" t="n">
-        <v>2.348</v>
+        <v>2.7784</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.8767</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1634</v>
+        <v>1.3231</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1749</v>
+        <v>0.2292</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3382</v>
+        <v>1.0939</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R18" t="n">
-        <v>2.722</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3548</v>
+        <v>1.3043</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.7336</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2731</v>
+        <v>0.5707</v>
       </c>
       <c r="V18" t="n">
-        <v>1.639</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>5.4633</v>
+        <v>0.0863</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.8243</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0051</v>
+        <v>0.3109</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3284</v>
+        <v>1.5349</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3335</v>
+        <v>-1.224</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.065</v>
+        <v>1.5177</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2308</v>
+        <v>0.6061</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2958</v>
+        <v>0.9116</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1585</v>
+        <v>1.3887</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1212</v>
+        <v>0.7929</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.5958</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2236</v>
+        <v>0.129</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1096</v>
+        <v>-0.1868</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3331</v>
+        <v>0.3159</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2574</v>
+        <v>-0.1173</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4869</v>
+        <v>0.1462</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7443</v>
+        <v>-0.2636</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0759</v>
+        <v>0.1127</v>
       </c>
       <c r="E20" t="n">
-        <v>1.185</v>
+        <v>-0.2116</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2609</v>
+        <v>0.3242</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5191</v>
+        <v>-0.055</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6075</v>
+        <v>0.2353</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9116</v>
+        <v>-0.2902</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3936</v>
+        <v>0.1579</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7966</v>
+        <v>0.1207</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5971</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1255</v>
+        <v>-0.2129</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1891</v>
+        <v>0.1146</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3145</v>
+        <v>-0.3275</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5024</v>
+        <v>0.345</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>-0.3695</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2937</v>
+        <v>0.7145</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1063</v>
+        <v>0.0717</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3466</v>
+        <v>-1.0049</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2402</v>
+        <v>1.0767</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2609</v>
+        <v>-0.7682</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2396</v>
+        <v>-1.8583</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0213</v>
+        <v>1.0902</v>
       </c>
       <c r="J21" t="n">
-        <v>0.349</v>
+        <v>-0.712</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3117</v>
+        <v>-1.4414</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>0.7294</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6099</v>
+        <v>-0.0562</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5513</v>
+        <v>-0.4169</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0586</v>
+        <v>0.3608</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8351</v>
+        <v>0.0871</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4386</v>
+        <v>-0.2929</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3965</v>
+        <v>0.3801</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2462</v>
+        <v>-0.1084</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4584</v>
+        <v>-1.6361</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2122</v>
+        <v>1.5277</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7645</v>
+        <v>-1.7321</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.86</v>
+        <v>0.2208</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0955</v>
+        <v>-1.953</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6933</v>
+        <v>-1.6195</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4342</v>
+        <v>0.6378</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7409</v>
+        <v>-2.2572</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0712</v>
+        <v>-0.1127</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3546</v>
+        <v>0.3043</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2284</v>
+        <v>0.3066</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7652</v>
+        <v>-0.1258</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.4324</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8511</v>
+        <v>-0.2493</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3219</v>
+        <v>-0.468</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4708</v>
+        <v>0.2187</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7363</v>
+        <v>-0.255</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2149</v>
+        <v>-0.2357</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9512</v>
+        <v>-0.0193</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6064</v>
+        <v>0.3475</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6407</v>
+        <v>0.3103</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2471</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1299</v>
+        <v>-0.6025</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4258</v>
+        <v>-0.546</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2959</v>
+        <v>-0.0565</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4343</v>
+        <v>0.6886</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>0.3227</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4004</v>
+        <v>0.3659</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7457</v>
+        <v>-1.3097</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2702</v>
+        <v>-3.5457</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5245</v>
+        <v>2.236</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1263</v>
+        <v>-1.5049</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4704</v>
+        <v>-4.1667</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5967</v>
+        <v>2.6618</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1028</v>
+        <v>-1.8371</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8485</v>
+        <v>-3.7209</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9513</v>
+        <v>1.8837</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0236</v>
+        <v>0.3322</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3781</v>
+        <v>-0.4458</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3546</v>
+        <v>0.778</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1558</v>
+        <v>0.382</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0333</v>
+        <v>0.0717</v>
       </c>
       <c r="U24" t="n">
-        <v>0.189</v>
+        <v>0.3104</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3214</v>
+        <v>1.6342</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4073</v>
+        <v>-1.3544</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0824</v>
+        <v>-2.0563</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6751</v>
+        <v>0.7019</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4886</v>
+        <v>-1.1352</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.1541</v>
+        <v>0.471</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6655</v>
+        <v>-1.6062</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7987</v>
+        <v>-1.1224</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.6965</v>
+        <v>0.8446</v>
       </c>
       <c r="L25" t="n">
-        <v>1.8977</v>
+        <v>-1.967</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3102</v>
+        <v>-0.0129</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4576</v>
+        <v>-0.3736</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7678</v>
+        <v>0.3608</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7431</v>
+        <v>0.5517</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5202</v>
+        <v>0.2042</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2229</v>
+        <v>0.3474</v>
       </c>
       <c r="V25" t="n">
-        <v>1.639</v>
+        <v>-0.3155</v>
       </c>
       <c r="W25" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5242</v>
+        <v>-5.5196</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1374</v>
+        <v>-0.3575</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.6616</v>
+        <v>-5.1621</v>
       </c>
       <c r="G26" t="n">
-        <v>1.5735</v>
+        <v>1.5715</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5845</v>
+        <v>0.5777</v>
       </c>
       <c r="I26" t="n">
-        <v>0.989</v>
+        <v>0.9938</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7702</v>
+        <v>1.7567</v>
       </c>
       <c r="K26" t="n">
-        <v>1.1358</v>
+        <v>1.1236</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1967</v>
+        <v>-0.1852</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0197</v>
+        <v>0.0196</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4748</v>
+        <v>0.0044</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4552</v>
+        <v>0.0152</v>
       </c>
       <c r="V26" t="n">
-        <v>-5.3026</v>
+        <v>-5.2896</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.4633</v>
+        <v>-5.4474</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>8.5029</v>
+        <v>10.8831</v>
       </c>
       <c r="E27" t="n">
-        <v>1.688300000000001</v>
+        <v>1.391</v>
       </c>
       <c r="F27" t="n">
-        <v>6.814400000000001</v>
+        <v>9.492100000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>8.340499999999997</v>
+        <v>8.329699999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>5.981299999999999</v>
+        <v>5.960800000000002</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3591</v>
+        <v>2.369</v>
       </c>
       <c r="J27" t="n">
-        <v>5.079899999999999</v>
+        <v>4.863099999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>9.612</v>
+        <v>9.484799999999998</v>
       </c>
       <c r="L27" t="n">
-        <v>-4.532199999999999</v>
+        <v>-4.621899999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>3.260600000000001</v>
+        <v>3.466399999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>-3.6307</v>
+        <v>-3.524</v>
       </c>
       <c r="O27" t="n">
-        <v>6.891300000000001</v>
+        <v>6.990800000000002</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.1343</v>
+        <v>-1.1383</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.8784</v>
+        <v>-15.9343</v>
       </c>
       <c r="R27" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S27" t="n">
-        <v>4.1889</v>
+        <v>6.5731</v>
       </c>
       <c r="T27" t="n">
-        <v>1.5276</v>
+        <v>1.5525</v>
       </c>
       <c r="U27" t="n">
-        <v>2.6613</v>
+        <v>5.0207</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.8923</v>
+        <v>-2.8814</v>
       </c>
       <c r="W27" t="n">
-        <v>10.9589</v>
+        <v>10.9096</v>
       </c>
       <c r="X27" t="n">
-        <v>-13.8514</v>
+        <v>-13.7913</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104574_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104574_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-9.8202</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-5.4474</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104574_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-13.7913</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
